--- a/大會師總戰報_20260625/🎨_全策略大會師總表_20260625.xlsx
+++ b/大會師總戰報_20260625/🎨_全策略大會師總表_20260625.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -540,12 +540,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2425.TW</t>
+          <t>2404.TW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>承啟</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -554,13 +554,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>42.35</v>
+        <v>1365</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="F4" t="n">
-        <v>6492</v>
+        <v>5926</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -571,12 +571,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2404.TW</t>
+          <t>2425.TW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>承啟</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1365</v>
+        <v>42.35</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="F5" t="n">
-        <v>5926</v>
+        <v>6492</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -602,12 +602,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2892.TW</t>
+          <t>2458.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -616,13 +616,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32.85</v>
+        <v>180</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="F6" t="n">
-        <v>59028</v>
+        <v>13582</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -664,12 +664,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2458.TW</t>
+          <t>2892.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -678,13 +678,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>180</v>
+        <v>32.85</v>
       </c>
       <c r="E8" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="F8" t="n">
-        <v>13582</v>
+        <v>59028</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -695,12 +695,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5434.TW</t>
+          <t>5230.TWO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>雷笛克光學</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -709,13 +709,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>505</v>
+        <v>21.85</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="F9" t="n">
-        <v>1358</v>
+        <v>1565</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -726,12 +726,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4976.TW</t>
+          <t>3406.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>佳凌</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -740,13 +740,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>42.35</v>
+        <v>759</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="F10" t="n">
-        <v>9908</v>
+        <v>4169</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -757,12 +757,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5230.TWO</t>
+          <t>4128.TWO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>雷笛克光學</t>
+          <t>中天</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -771,13 +771,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>21.85</v>
+        <v>15.5</v>
       </c>
       <c r="E11" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="F11" t="n">
-        <v>1565</v>
+        <v>3840</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -788,12 +788,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4128.TWO</t>
+          <t>4976.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>中天</t>
+          <t>佳凌</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -802,13 +802,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.5</v>
+        <v>42.35</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="F12" t="n">
-        <v>3840</v>
+        <v>9908</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -819,12 +819,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3406.TW</t>
+          <t>8936.TWO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>國統</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>759</v>
+        <v>59.3</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="F13" t="n">
-        <v>4169</v>
+        <v>6386</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -881,12 +881,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8936.TWO</t>
+          <t>5434.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>國統</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -895,13 +895,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>59.3</v>
+        <v>505</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="F15" t="n">
-        <v>6386</v>
+        <v>1358</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -1036,12 +1036,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2316.TW</t>
+          <t>3008.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>楠梓電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>234.5</v>
+        <v>5165</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F20" t="n">
-        <v>4055</v>
+        <v>3393</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -1067,12 +1067,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2010.TW</t>
+          <t>2886.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>春源</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1081,13 +1081,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>24.45</v>
+        <v>46.65</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="F21" t="n">
-        <v>2101</v>
+        <v>62106</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3037.TW</t>
+          <t>2883.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1112,13 +1112,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1020</v>
+        <v>30.5</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="F22" t="n">
-        <v>34393</v>
+        <v>58570</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -1129,12 +1129,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3034.TW</t>
+          <t>2880.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>561</v>
+        <v>38</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>6314</v>
+        <v>52720</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -1160,12 +1160,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3008.TW</t>
+          <t>2812.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>台中銀</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1174,13 +1174,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>5165</v>
+        <v>20.05</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>3393</v>
+        <v>15523</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -1191,12 +1191,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2886.TW</t>
+          <t>2855.TW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>統一證</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>46.65</v>
+        <v>50.4</v>
       </c>
       <c r="E25" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="F25" t="n">
-        <v>62106</v>
+        <v>6663</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -1222,12 +1222,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2880.TW</t>
+          <t>2010.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>春源</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>38</v>
+        <v>24.45</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F26" t="n">
-        <v>52720</v>
+        <v>2101</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -1253,12 +1253,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2883.TW</t>
+          <t>2476.TW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>30.5</v>
+        <v>130.5</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="F27" t="n">
-        <v>58570</v>
+        <v>5938</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -1284,12 +1284,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2855.TW</t>
+          <t>2316.TW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>統一證</t>
+          <t>楠梓電</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1298,13 +1298,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>50.4</v>
+        <v>234.5</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F28" t="n">
-        <v>6663</v>
+        <v>4055</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -1315,27 +1315,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2812.TW</t>
+          <t>4178.TW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>台中銀</t>
+          <t>永笙-KY</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>老余裸K_賺賠比精選</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>20.05</v>
+        <v>18.15</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>15523</v>
+        <v>858</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
@@ -1346,12 +1346,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2476.TW</t>
+          <t>3189.TW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1360,13 +1360,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>130.5</v>
+        <v>812</v>
       </c>
       <c r="E30" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="F30" t="n">
-        <v>5938</v>
+        <v>44410</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
@@ -1377,12 +1377,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4716.TWO</t>
+          <t>4904.TW</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>大立</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1391,13 +1391,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>24.2</v>
+        <v>108.5</v>
       </c>
       <c r="E31" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="F31" t="n">
-        <v>5379</v>
+        <v>33493</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -1408,27 +1408,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4178.TW</t>
+          <t>4716.TWO</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>永笙-KY</t>
+          <t>大立</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>18.15</v>
+        <v>24.2</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="F32" t="n">
-        <v>858</v>
+        <v>5379</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
@@ -1439,12 +1439,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5392.TWO</t>
+          <t>3290.TWO</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>能率</t>
+          <t>東浦</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1453,13 +1453,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>45.75</v>
+        <v>71.3</v>
       </c>
       <c r="E33" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="F33" t="n">
-        <v>14803</v>
+        <v>3098</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
@@ -1470,12 +1470,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4904.TW</t>
+          <t>3034.TW</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>108.5</v>
+        <v>561</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F34" t="n">
-        <v>33493</v>
+        <v>6314</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
@@ -1501,27 +1501,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3709.TWO</t>
+          <t>3037.TW</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>鑫聯大投控</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>76</v>
+        <v>1020</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="F35" t="n">
-        <v>921</v>
+        <v>34393</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
@@ -1532,12 +1532,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3290.TWO</t>
+          <t>5876.TW</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>東浦</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1546,13 +1546,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>71.3</v>
+        <v>42</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F36" t="n">
-        <v>3098</v>
+        <v>13442</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
@@ -1563,12 +1563,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3189.TW</t>
+          <t>5515.TW</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>建國</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1577,13 +1577,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>812</v>
+        <v>39.9</v>
       </c>
       <c r="E37" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="F37" t="n">
-        <v>44410</v>
+        <v>2099</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
@@ -1594,12 +1594,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5876.TW</t>
+          <t>5483.TWO</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>上海商銀</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1608,13 +1608,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>42</v>
+        <v>174.5</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>13442</v>
+        <v>16711</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
@@ -1625,12 +1625,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5515.TW</t>
+          <t>5392.TWO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>建國</t>
+          <t>能率</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1639,13 +1639,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>39.9</v>
+        <v>45.75</v>
       </c>
       <c r="E39" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="F39" t="n">
-        <v>2099</v>
+        <v>14803</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
@@ -1656,12 +1656,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5483.TWO</t>
+          <t>6186.TWO</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>新潤</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1670,13 +1670,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>174.5</v>
+        <v>41.95</v>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F40" t="n">
-        <v>16711</v>
+        <v>1152</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
@@ -1687,27 +1687,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5439.TWO</t>
+          <t>6488.TWO</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>323</v>
+        <v>1040</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="F41" t="n">
-        <v>1464</v>
+        <v>1320</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -1718,12 +1718,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6186.TWO</t>
+          <t>6781.TW</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>新潤</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>41.95</v>
+        <v>1190</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="F42" t="n">
-        <v>1152</v>
+        <v>1059</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
@@ -1749,27 +1749,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6488.TWO</t>
+          <t>6139.TW</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>ABC突破切線精選</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1040</v>
+        <v>875</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="F43" t="n">
-        <v>1320</v>
+        <v>7511</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
@@ -1780,12 +1780,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6781.TW</t>
+          <t>7777.TWO</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>能率亞洲</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1794,13 +1794,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1190</v>
+        <v>44.4</v>
       </c>
       <c r="E44" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="F44" t="n">
-        <v>1059</v>
+        <v>7248</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
@@ -1811,12 +1811,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6139.TW</t>
+          <t>8042.TWO</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1825,13 +1825,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>875</v>
+        <v>200.5</v>
       </c>
       <c r="E45" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F45" t="n">
-        <v>7511</v>
+        <v>1226</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
@@ -1842,12 +1842,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7777.TWO</t>
+          <t>8044.TWO</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>能率亞洲</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1856,13 +1856,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>44.4</v>
+        <v>30.5</v>
       </c>
       <c r="E46" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>7248</v>
+        <v>2004</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
@@ -1873,27 +1873,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>8042.TWO</t>
+          <t>8110.TW</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ABC突破切線精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>200.5</v>
+        <v>63.2</v>
       </c>
       <c r="E47" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="F47" t="n">
-        <v>1226</v>
+        <v>57977</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
@@ -1904,12 +1904,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8044.TWO</t>
+          <t>9907.TW</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>統一實</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1918,13 +1918,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>30.5</v>
+        <v>15.4</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F48" t="n">
-        <v>2004</v>
+        <v>7560</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
@@ -1935,12 +1935,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8110.TW</t>
+          <t>9914.TW</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>美利達</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1949,13 +1949,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>63.2</v>
+        <v>72.8</v>
       </c>
       <c r="E49" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="F49" t="n">
-        <v>57977</v>
+        <v>578</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
@@ -1966,12 +1966,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>9907.TW</t>
+          <t>9921.TW</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>統一實</t>
+          <t>巨大</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1980,13 +1980,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>15.4</v>
+        <v>74.5</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F50" t="n">
-        <v>7560</v>
+        <v>1081</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
@@ -1997,12 +1997,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>9914.TW</t>
+          <t>9933.TW</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>美利達</t>
+          <t>中鼎</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2011,79 +2011,17 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>72.8</v>
+        <v>43.65</v>
       </c>
       <c r="E51" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="F51" t="n">
-        <v>578</v>
+        <v>3498</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>9921.TW</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>巨大</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>回後買上漲基礎版</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F52" t="n">
-        <v>1081</v>
-      </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>9933.TW</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>回後買上漲基礎版</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>43.65</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F53" t="n">
-        <v>3498</v>
-      </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="n">
         <v>1</v>
       </c>
     </row>
